--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T20:31:09+00:00</t>
+    <t>2026-09-14T10:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:59:28+00:00</t>
+    <t>2026-09-14T11:54:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:54:38+00:00</t>
+    <t>2026-09-14T13:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:10:06+00:00</t>
+    <t>2026-09-14T14:30:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T14:30:50+00:00</t>
+    <t>2026-09-14T14:45:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T14:45:51+00:00</t>
+    <t>2026-09-14T16:08:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:08:05+00:00</t>
+    <t>2026-09-14T16:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
+++ b/CodeSystem-mii-cs-mikrobio-susceptibility-norm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T16:39:15+00:00</t>
+    <t>2026-09-14T18:28:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
